--- a/data/submissions.xlsx
+++ b/data/submissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,74 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-01-03T13:17:02</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Aadhava</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>realtime_video</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>53</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-02-20T08:55:13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aadhava</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nay</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>realtime_video</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
